--- a/model_inputs.xlsx
+++ b/model_inputs.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>72.76667260911114</v>
+        <v>68.44223262525097</v>
       </c>
     </row>
     <row r="5">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>70.5961826056292</v>
+        <v>66.40391354869665</v>
       </c>
     </row>
     <row r="6">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.06680184266498</v>
+        <v>17.66717436464856</v>
       </c>
     </row>
     <row r="7">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48.24297476214688</v>
+        <v>43.75758504444416</v>
       </c>
     </row>
     <row r="8">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60.53327096572978</v>
+        <v>56.27812172621351</v>
       </c>
     </row>
     <row r="9">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70.5961826056292</v>
+        <v>66.40391354869665</v>
       </c>
     </row>
     <row r="10">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82.54146032847098</v>
+        <v>78.53258275468221</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104.1381016190931</v>
+        <v>99.5022187489725</v>
       </c>
     </row>
     <row r="12">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="14">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.062</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="17">
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6374815328343255</v>
+        <v>0.3121255595375417</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04926084834757865</v>
+        <v>0.09592506801386291</v>
       </c>
       <c r="D19" t="n">
-        <v>0.696726818941931</v>
+        <v>0.3811842794139529</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04773113909993744</v>
+        <v>0.1034796418470033</v>
       </c>
     </row>
     <row r="20">
@@ -1211,510 +1211,168 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1777006229697089</v>
+        <v>0.2386394483702447</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02303962016318991</v>
+        <v>0.07802965815306369</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1776509607040344</v>
+        <v>0.246653822331999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01457115438170229</v>
+        <v>0.05625672234870883</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>terminal_g</t>
+          <t>cogs_pct</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.05393123402148427</v>
+        <v>0.1101131530868844</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01717912034703535</v>
+        <v>0.05496079633648594</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09792108547177895</v>
+        <v>0.1235220905333243</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01304308040020018</v>
+        <v>0.02824060298553159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cogs_shock_y5</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04114149622316007</v>
+        <v>0.06118017109160155</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01140633333416835</v>
+        <v>0.04322716038061424</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04846791748545595</v>
+        <v>0.07699511923741299</v>
       </c>
       <c r="E22" t="n">
-        <v>0.003986045225222163</v>
+        <v>0.016511737176788</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rev_shock_y5</t>
+          <t>terminal_g</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02448720115167703</v>
+        <v>0.04375969604728129</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009693586597735337</v>
+        <v>0.04621484527354247</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0301093268558088</v>
+        <v>0.0712202438947873</v>
       </c>
       <c r="E23" t="n">
-        <v>0.002564807641849491</v>
+        <v>0.01709766063844321</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sga_shock_y5</t>
+          <t>sga_pct</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02355905367085314</v>
+        <v>0.06613100498605616</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01088438609966649</v>
+        <v>0.04145937447382073</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02741898390366499</v>
+        <v>0.06932792945285959</v>
       </c>
       <c r="E24" t="n">
-        <v>0.002143665170800689</v>
+        <v>0.01619467001040475</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>capex_shock_y5</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0009970124954719708</v>
+        <v>0.003288918985574414</v>
       </c>
       <c r="C25" t="n">
-        <v>0.002250410522724775</v>
+        <v>0.0130307654617317</v>
       </c>
       <c r="D25" t="n">
-        <v>0.001430025436958178</v>
+        <v>0.004919540322804946</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0001529900748932361</v>
+        <v>0.001280537123976023</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cogs_shock_y1</t>
+          <t>tax_rate</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.970465215394659e-05</v>
+        <v>0.008518571765300314</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0008304242220364248</v>
+        <v>0.009869689978766144</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001727368067010074</v>
+        <v>0.002836484246535655</v>
       </c>
       <c r="E26" t="n">
-        <v>1.46219303492614e-05</v>
+        <v>0.0006915217115053975</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cogs_shock_y2</t>
+          <t>da_pct</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0002142449157000806</v>
+        <v>0.002341033390285302</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0007952221541449866</v>
+        <v>0.005656158278389971</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001643118599670617</v>
+        <v>0.001362779921985734</v>
       </c>
       <c r="E27" t="n">
-        <v>1.267057464057274e-05</v>
+        <v>0.0003597878285825851</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cogs_shock_y3</t>
+          <t>nwc</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0001078655828261597</v>
+        <v>-0.0008482811830354453</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0007160875777425871</v>
+        <v>0.002676266333652001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001567109002300089</v>
+        <v>0.0002099848543408216</v>
       </c>
       <c r="E28" t="n">
-        <v>1.223344724099562e-05</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cogs_shock_y4</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.0002342205966719557</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.000696716799363223</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.000150105494511351</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1.223700646423586e-05</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>rev_shock_y1</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.0001119822903807912</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.0005822695774468615</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0001110822703755962</v>
-      </c>
-      <c r="E30" t="n">
-        <v>9.488097062430104e-06</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>rev_shock_y2</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3.292567273968041e-05</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.0005764085984690145</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0001058384627523404</v>
-      </c>
-      <c r="E31" t="n">
-        <v>8.563651372966691e-06</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>rev_shock_y3</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0.0001389617860543324</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.0006709246918570992</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0001008383686065152</v>
-      </c>
-      <c r="E32" t="n">
-        <v>8.463389669017065e-06</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>sga_shock_y1</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>6.91888982047566e-05</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.000620906845019072</v>
-      </c>
-      <c r="D33" t="n">
-        <v>9.706644716156645e-05</v>
-      </c>
-      <c r="E33" t="n">
-        <v>7.693861398183032e-06</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>rev_shock_y4</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>7.683659208266078e-05</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.0005769857498271465</v>
-      </c>
-      <c r="D34" t="n">
-        <v>9.635156587555122e-05</v>
-      </c>
-      <c r="E34" t="n">
-        <v>7.066709651622204e-06</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sga_shock_y2</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>8.653932801341189e-05</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.0007025834608184468</v>
-      </c>
-      <c r="D35" t="n">
-        <v>9.242220955841973e-05</v>
-      </c>
-      <c r="E35" t="n">
-        <v>7.329747477485552e-06</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sga_shock_y3</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>8.655846118812979e-05</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.0005792274036814026</v>
-      </c>
-      <c r="D36" t="n">
-        <v>8.814483861437858e-05</v>
-      </c>
-      <c r="E36" t="n">
-        <v>6.727637716563988e-06</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sga_shock_y4</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.00011781526379873</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.0005058260512878804</v>
-      </c>
-      <c r="D37" t="n">
-        <v>8.429381308406826e-05</v>
-      </c>
-      <c r="E37" t="n">
-        <v>6.418348493745271e-06</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>nwc_shock_y5</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0.0001874649774218391</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.0004643886344145885</v>
-      </c>
-      <c r="D38" t="n">
-        <v>6.306086259386038e-05</v>
-      </c>
-      <c r="E38" t="n">
-        <v>6.653943355588048e-06</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>capex_shock_y1</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>2.623916045743298e-05</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.0002745240199278463</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.763196502174822e-05</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.440902386523946e-06</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>capex_shock_y2</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3.204347296980802e-05</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.0002397527013409212</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.676667226970143e-05</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.387495539178518e-06</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>capex_shock_y3</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>2.900684613775057e-05</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.0002436905474396836</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.598673135362359e-05</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1.297261272948311e-06</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>capex_shock_y4</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2.016524960186968e-05</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.0002402020124745801</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1.529435099327493e-05</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1.1192324506072e-06</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>nwc_shock_y1</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>-2.947189955220971e-06</v>
-      </c>
-      <c r="C43" t="n">
-        <v>5.548435142023264e-05</v>
-      </c>
-      <c r="D43" t="n">
-        <v>7.652319520515508e-07</v>
-      </c>
-      <c r="E43" t="n">
-        <v>6.315509837713198e-08</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>nwc_shock_y2</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>8.002741691897752e-07</v>
-      </c>
-      <c r="C44" t="n">
-        <v>5.526355488464338e-05</v>
-      </c>
-      <c r="D44" t="n">
-        <v>7.27286053356084e-07</v>
-      </c>
-      <c r="E44" t="n">
-        <v>5.619973608880612e-08</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>nwc_shock_y3</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2.033309244678524e-07</v>
-      </c>
-      <c r="C45" t="n">
-        <v>5.641558898425891e-05</v>
-      </c>
-      <c r="D45" t="n">
-        <v>6.944636622755037e-07</v>
-      </c>
-      <c r="E45" t="n">
-        <v>5.411831303365063e-08</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>nwc_shock_y4</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>4.375503691387998e-07</v>
-      </c>
-      <c r="C46" t="n">
-        <v>4.943583222647563e-05</v>
-      </c>
-      <c r="D46" t="n">
-        <v>6.633188649400711e-07</v>
-      </c>
-      <c r="E46" t="n">
-        <v>5.264023505609038e-08</v>
+        <v>4.696993602268518e-05</v>
       </c>
     </row>
   </sheetData>
